--- a/RIGEL/会社概要・資料/事業計画書・融資/事業計画書.xlsx
+++ b/RIGEL/会社概要・資料/事業計画書・融資/事業計画書.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">（　　　　　　　　　　）</t>
   </si>
   <si>
-    <t xml:space="preserve">事業者</t>
+    <t xml:space="preserve">株式会社RIGEL</t>
   </si>
   <si>
     <t xml:space="preserve">（  　　　　　　　　　）</t>
@@ -613,7 +613,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
+  <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -637,10 +637,6 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="102">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -691,7 +687,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -819,19 +815,19 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="15" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -847,15 +843,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="15" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -887,11 +883,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="15" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -899,7 +895,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -911,15 +907,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="21" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -931,19 +927,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="23" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="22" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="24" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="25" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -959,7 +955,7 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -967,7 +963,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="26" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1052,14 +1048,13 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Excel Built-in Comma [0]" xfId="20"/>
   </cellStyles>
   <colors>
     <indexedColors>

--- a/RIGEL/会社概要・資料/事業計画書・融資/事業計画書.xlsx
+++ b/RIGEL/会社概要・資料/事業計画書・融資/事業計画書.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="97">
   <si>
     <t xml:space="preserve">事業計画書</t>
   </si>
@@ -62,10 +62,16 @@
     <t xml:space="preserve">住　所</t>
   </si>
   <si>
+    <t xml:space="preserve">千葉県柏市</t>
+  </si>
+  <si>
     <t xml:space="preserve"> その他</t>
   </si>
   <si>
     <t xml:space="preserve">（　　　　　　　　　　）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">事業者</t>
   </si>
   <si>
     <t xml:space="preserve">株式会社RIGEL</t>
@@ -1492,12 +1498,14 @@
       <c r="I9" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="26"/>
+      <c r="J9" s="26" t="s">
+        <v>12</v>
+      </c>
       <c r="K9" s="26"/>
       <c r="L9" s="26"/>
       <c r="M9" s="26"/>
       <c r="O9" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
@@ -1518,7 +1526,7 @@
       <c r="O10" s="15"/>
       <c r="P10" s="16"/>
       <c r="Q10" s="24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R10" s="24"/>
       <c r="S10" s="10"/>
@@ -1530,16 +1538,18 @@
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11"/>
       <c r="I11" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="27"/>
+        <v>15</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>16</v>
+      </c>
       <c r="K11" s="27"/>
       <c r="L11" s="27"/>
       <c r="M11" s="27"/>
       <c r="O11" s="28"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="24" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R11" s="24"/>
       <c r="S11" s="10"/>
@@ -1571,15 +1581,15 @@
       <c r="L13" s="32"/>
       <c r="M13" s="33"/>
       <c r="O13" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W13" s="34" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="35" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B14" s="35"/>
       <c r="C14" s="35"/>
@@ -1597,27 +1607,27 @@
       <c r="P14" s="36"/>
       <c r="Q14" s="36"/>
       <c r="R14" s="37" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S14" s="38" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T14" s="38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U14" s="38" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V14" s="39" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="W14" s="40" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="41" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="41"/>
@@ -1635,27 +1645,27 @@
       <c r="P15" s="36"/>
       <c r="Q15" s="36"/>
       <c r="R15" s="29" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S15" s="29" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T15" s="29" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="U15" s="29" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="V15" s="29" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W15" s="42" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="43" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16" s="43"/>
       <c r="C16" s="43"/>
@@ -1670,7 +1680,7 @@
       <c r="L16" s="43"/>
       <c r="M16" s="43"/>
       <c r="O16" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
@@ -1691,7 +1701,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="48" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
@@ -1706,7 +1716,7 @@
       <c r="L17" s="48"/>
       <c r="M17" s="48"/>
       <c r="O17" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
@@ -1741,7 +1751,7 @@
       <c r="M18" s="48"/>
       <c r="O18" s="49"/>
       <c r="P18" s="50" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q18" s="50"/>
       <c r="R18" s="44"/>
@@ -1766,7 +1776,7 @@
       <c r="L19" s="48"/>
       <c r="M19" s="48"/>
       <c r="O19" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P19" s="9"/>
       <c r="Q19" s="9"/>
@@ -1810,7 +1820,7 @@
       <c r="L20" s="48"/>
       <c r="M20" s="48"/>
       <c r="O20" s="54" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P20" s="54"/>
       <c r="Q20" s="54"/>
@@ -1835,7 +1845,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="55" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B21" s="55"/>
       <c r="C21" s="55"/>
@@ -1851,7 +1861,7 @@
       <c r="M21" s="55"/>
       <c r="O21" s="15"/>
       <c r="P21" s="56" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q21" s="56"/>
       <c r="R21" s="44"/>
@@ -1871,7 +1881,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="57" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B22" s="57"/>
       <c r="C22" s="57"/>
@@ -1888,7 +1898,7 @@
       <c r="O22" s="11"/>
       <c r="P22" s="58"/>
       <c r="Q22" s="50" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="R22" s="44"/>
       <c r="S22" s="44"/>
@@ -1921,7 +1931,7 @@
       <c r="M23" s="57"/>
       <c r="O23" s="11"/>
       <c r="P23" s="59" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q23" s="59"/>
       <c r="R23" s="44"/>
@@ -1946,7 +1956,7 @@
       <c r="L24" s="57"/>
       <c r="M24" s="57"/>
       <c r="O24" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P24" s="9"/>
       <c r="Q24" s="9"/>
@@ -1991,7 +2001,7 @@
       <c r="M25" s="57"/>
       <c r="O25" s="60"/>
       <c r="P25" s="56" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q25" s="56"/>
       <c r="R25" s="44"/>
@@ -2017,7 +2027,7 @@
       <c r="M26" s="57"/>
       <c r="O26" s="11"/>
       <c r="P26" s="63" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q26" s="63"/>
       <c r="R26" s="44"/>
@@ -2042,7 +2052,7 @@
       <c r="L27" s="57"/>
       <c r="M27" s="57"/>
       <c r="O27" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
@@ -2073,13 +2083,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="65" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B28" s="65"/>
       <c r="C28" s="65"/>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="66"/>
@@ -2090,7 +2100,7 @@
       <c r="L28" s="66"/>
       <c r="M28" s="66"/>
       <c r="O28" s="54" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P28" s="54"/>
       <c r="Q28" s="54"/>
@@ -2116,7 +2126,7 @@
       <c r="L29" s="66"/>
       <c r="M29" s="66"/>
       <c r="O29" s="54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P29" s="54"/>
       <c r="Q29" s="54"/>
@@ -2142,7 +2152,7 @@
       <c r="L30" s="66"/>
       <c r="M30" s="66"/>
       <c r="O30" s="60" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P30" s="60"/>
       <c r="Q30" s="60"/>
@@ -2173,13 +2183,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="54" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B31" s="54"/>
       <c r="C31" s="54"/>
       <c r="D31" s="54"/>
       <c r="E31" s="70" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F31" s="70"/>
       <c r="G31" s="70"/>
@@ -2190,7 +2200,7 @@
       <c r="L31" s="70"/>
       <c r="M31" s="70"/>
       <c r="O31" s="71" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P31" s="71"/>
       <c r="Q31" s="71"/>
@@ -2212,7 +2222,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="70"/>
@@ -2225,7 +2235,7 @@
       <c r="L32" s="70"/>
       <c r="M32" s="70"/>
       <c r="O32" s="54" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P32" s="54"/>
       <c r="Q32" s="54"/>
@@ -2247,7 +2257,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="70"/>
@@ -2260,7 +2270,7 @@
       <c r="L33" s="70"/>
       <c r="M33" s="70"/>
       <c r="O33" s="54" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P33" s="54"/>
       <c r="Q33" s="54"/>
@@ -2293,7 +2303,7 @@
       <c r="A34" s="11"/>
       <c r="B34" s="29"/>
       <c r="C34" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="70"/>
@@ -2312,7 +2322,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="70"/>
@@ -2342,15 +2352,15 @@
       <c r="L36" s="70"/>
       <c r="M36" s="70"/>
       <c r="O36" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="W36" s="34" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="54" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B37" s="54"/>
       <c r="C37" s="54"/>
@@ -2368,29 +2378,29 @@
       <c r="P37" s="36"/>
       <c r="Q37" s="36"/>
       <c r="R37" s="37" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S37" s="38" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T37" s="38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U37" s="38" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V37" s="39" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="W37" s="40" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15"/>
       <c r="B38" s="16"/>
       <c r="C38" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="77"/>
@@ -2406,22 +2416,22 @@
       <c r="P38" s="36"/>
       <c r="Q38" s="36"/>
       <c r="R38" s="29" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="S38" s="29" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T38" s="29" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="U38" s="29" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="V38" s="29" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W38" s="42" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2430,7 +2440,7 @@
         <v>2</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="77"/>
@@ -2443,7 +2453,7 @@
       <c r="L39" s="77"/>
       <c r="M39" s="77"/>
       <c r="O39" s="78" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P39" s="24"/>
       <c r="Q39" s="24"/>
@@ -2458,7 +2468,7 @@
       <c r="A40" s="11"/>
       <c r="B40" s="16"/>
       <c r="C40" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="77"/>
@@ -2486,7 +2496,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="77"/>
@@ -2514,7 +2524,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="77"/>
@@ -2542,7 +2552,7 @@
         <v>2</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="77"/>
@@ -2592,7 +2602,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -2607,7 +2617,7 @@
       <c r="L45" s="10"/>
       <c r="M45" s="10"/>
       <c r="O45" s="38" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P45" s="38"/>
       <c r="Q45" s="38"/>
@@ -2640,7 +2650,7 @@
       <c r="A46" s="15"/>
       <c r="B46" s="16"/>
       <c r="C46" s="54" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D46" s="54"/>
       <c r="E46" s="10"/>
@@ -2653,7 +2663,7 @@
       <c r="L46" s="10"/>
       <c r="M46" s="10"/>
       <c r="O46" s="38" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P46" s="38"/>
       <c r="Q46" s="38"/>
@@ -2670,7 +2680,7 @@
         <v>2</v>
       </c>
       <c r="C47" s="54" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D47" s="54"/>
       <c r="E47" s="10"/>
@@ -2683,7 +2693,7 @@
       <c r="L47" s="10"/>
       <c r="M47" s="10"/>
       <c r="O47" s="38" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P47" s="38"/>
       <c r="Q47" s="38"/>
@@ -2704,7 +2714,7 @@
       <c r="A48" s="11"/>
       <c r="B48" s="16"/>
       <c r="C48" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="10"/>
@@ -2717,7 +2727,7 @@
       <c r="L48" s="10"/>
       <c r="M48" s="10"/>
       <c r="O48" s="38" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P48" s="38"/>
       <c r="Q48" s="38"/>
@@ -2780,12 +2790,12 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="59" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B53" s="59"/>
       <c r="C53" s="59"/>
@@ -2802,7 +2812,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="85" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B54" s="85"/>
       <c r="C54" s="85"/>
@@ -2864,7 +2874,7 @@
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="59" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B58" s="59"/>
       <c r="C58" s="59"/>
@@ -2881,7 +2891,7 @@
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="85" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B59" s="85"/>
       <c r="C59" s="85"/>
@@ -2978,7 +2988,7 @@
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="59" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B65" s="59"/>
       <c r="C65" s="59"/>
@@ -2995,7 +3005,7 @@
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="85" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B66" s="85"/>
       <c r="C66" s="85"/>
@@ -3057,7 +3067,7 @@
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="59" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B70" s="59"/>
       <c r="C70" s="59"/>
@@ -3074,7 +3084,7 @@
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="85" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B71" s="85"/>
       <c r="C71" s="85"/>
@@ -3167,12 +3177,12 @@
     <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="59" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B79" s="59"/>
       <c r="C79" s="59"/>
@@ -3249,7 +3259,7 @@
     </row>
     <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="87" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B84" s="88"/>
       <c r="C84" s="88"/>
@@ -3326,7 +3336,7 @@
     </row>
     <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="59" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B89" s="59"/>
       <c r="C89" s="59"/>
@@ -3409,7 +3419,7 @@
     </row>
     <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3429,7 +3439,7 @@
     </row>
     <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="90" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B98" s="90"/>
       <c r="C98" s="91"/>
@@ -3461,7 +3471,7 @@
     </row>
     <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="94" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B100" s="94"/>
       <c r="C100" s="91"/>
@@ -3508,7 +3518,7 @@
     </row>
     <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="94" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B103" s="94"/>
       <c r="C103" s="97"/>
@@ -3518,7 +3528,7 @@
       <c r="G103" s="97"/>
       <c r="H103" s="99"/>
       <c r="J103" s="100" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K103" s="98"/>
       <c r="L103" s="98"/>
